--- a/medford_telezhki_endoskopicheskie.xlsx
+++ b/medford_telezhki_endoskopicheskie.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Тележки эндоскопические для оснащения клиник и медицинских учреждений. В каталоге представлено 2 позиций.</t>
+          <t>Тележки эндоскопические для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_telezhki_endoskopicheskie.xlsx
+++ b/medford_telezhki_endoskopicheskie.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать тележки эндоскопические для клиники?</t>
+          <t>Что размещают на эндоскопической тележке?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (технические параметры). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>На стойке компактно размещают компоненты эндоскопической системы: видеопроцессор, источник света, монитор, аспиратор, а также вспомогательные блоки и аксессуары. Многоуровневая конструкция даёт эргономичный доступ ко всему необходимому во время исследования и позволяет перевозить комплекс как единое целое.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем тележка отличается от стационарной стойки?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Тележка мобильна: поворотные колёса позволяют перемещать оборудование между кабинетами, операционными и зоной обработки. Два колеса по диагонали обычно с тормозом для фиксации на месте. Стационарные решения привязаны к точке, тогда как тележка сокращает время подготовки за счёт быстрого перемещения всего набора.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Как понять, что тележка подойдёт к нашему оборудованию?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>Проверьте совместимость по габаритам, весу и расположению разъёмов используемых приборов. Число полок должно соответствовать количеству блоков, а нагрузка на ярус — их массе. При замене стойки в готовом кабинете сверьте посадочные размеры процессора, источника света и монитора.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Сколько полок нужно?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Число ярусов определяется количеством подключаемых блоков и запасом под расходники. Каждому основному прибору отводят свою полку с запасом по нагрузке; тяжёлые блоки ставят ниже для устойчивости. Точную конфигурацию подбирают под конкретный набор оборудования клиники.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Из каких материалов делают тележки?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Применяют антикоррозионные материалы: сталь с порошковым покрытием, алюминий, ударопрочный пластик. Они выдерживают дезинфицирующие растворы и сохраняют гигиеничность. Гладкие поверхности без лишних стыков облегчают санитарную обработку, что важно при регулярном использовании в эндоскопии.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что входит в эндоскопическую стойку?</t>
+          <t>Нужны ли крепления под монитор и кабели?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Кронштейн под монитор поднимает экран на уровень взгляда и освобождает полки, а держатели и направляющие для проводов убирают кабели из рабочей зоны. Эти элементы ускоряют подготовку к исследованию, упрощают уборку и снижают риск повреждения кабелей при перемещении.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопия простыми словами?</t>
+          <t>Требуется ли регистрационное удостоверение?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Оснащение медицинского кабинета проводят изделиями с действующими разрешительными документами. Уточните наличие регистрационного удостоверения Росздравнадзора на конкретную модель стойки, если она классифицируется как медицинское изделие, и запросите документ у поставщика до закупки.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Как обслуживать эндоскопическую тележку?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Основной уход — регулярная санитарная обработка поверхностей совместимыми дезинфектантами и контроль состояния колёсных опор и тормозов. Периодически проверяют затяжку креплений и целостность держателей кабеля. Простая конструкция стойки делает обслуживание несложным при соблюдении режима очистки.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>telezhki_endoskopicheskie</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Тележки эндоскопические для оснащения клиник и медицинских учреждений.</t>
+          <t>Тележки эндоскопические — мобильные приборные стойки для размещения, организации и безопасного перемещения компонентов эндоскопической системы внутри клиники. На них компактно ставят видеопроцессор, источник света, монитор, аспиратор и вспомогательные блоки, а колёсная база позволяет перевозить комплекс между кабинетами и зоной обработки. В каталоге представлены стойки Medtrade СМПП-01 и СМПП-02. Конструкция с несколькими уровнями и держателями кабеля упрощает доступ к оборудованию во время исследования и его санитарную обработку.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Виды эндоскопических тележек</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2716,7 +2754,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое тележки эндоскопические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -2992,51 +3030,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Виды эндоскопических тележек</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Вид</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Конструкция</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Область применения</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Стойка медицинская приборная (СМПП-02) Medtrade</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Базовые</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Несколько уровней для хранения оборудования</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Хранение и перемещение приборов</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Стойка медицинская приборная СМПП-01 Medtrade</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>Модульные функциональные</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Кронштейны под мониторы, интеграция кабелей и освещения</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Полноценное рабочее место эндоскописта</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Узкоспециализированные</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Адаптированы под профильный комплект</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Гастроэнтерология, урология, бронхоскопия</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Контейнерные</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Лотки и контейнеры для эндоскопов</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Транспортировка и хранение эндоскопов</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3048,7 +3144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3374,12 +3470,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Составьте перечень оборудования</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается тележки эндоскопические: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Определите, какие блоки встанут на стойку: видеопроцессор, источник света, монитор, аспиратор, вспомогательные модули. От их числа и суммарного веса зависит требуемое количество полок и допустимая нагрузка на каждый ярус. Список компонентов — отправная точка подбора тележки.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3419,12 +3515,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Проверьте совместимость по габаритам</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Убедитесь, что приборы встают по размерам и весу, а расположение разъёмов и кабелей позволяет подключить их без натяжения. Совместимость с используемой эндоскопической системой проверяют до покупки, особенно при замене стойки в готовом кабинете.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3464,12 +3560,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Оцените число полок и нагрузку</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: технические характеристики. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Многоуровневые стойки обычно несут несколько ярусов. Выбирайте конфигурацию так, чтобы каждый блок имел свою полку с запасом по нагрузке. Тяжёлый источник света и процессор ставят ниже для устойчивости, монитор — на кронштейн или верхний уровень.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3509,12 +3605,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Учтите крепления и кабель-менеджмент</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Держатели кабеля, кронштейн под монитор, места под ёмкости и инструменты снижают беспорядок и ускоряют подготовку к исследованию. Продуманная разводка проводов упрощает уборку и уменьшает риск повреждения кабелей при перемещении.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3554,12 +3650,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте устойчивость и мобильность</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Поворотные колёса с резиновым ободом и тормозом на двух колёсах по диагонали обеспечивают перемещение и надёжную фиксацию на месте. Устойчивость особенно важна, если стойку катают между кабинетами и операционными по неровным полам и порогам.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3599,12 +3695,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Оцените материалы и обработку</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Поверхности должны легко очищаться и выдерживать дезинфицирующие растворы. Антикоррозионные материалы — сталь с порошковым покрытием, алюминий, ударопрочный пластик — сохраняют вид и гигиеничность при регулярной санитарной обработке. Гладкая конструкция без лишних стыков предпочтительна.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3654,7 +3750,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Тележки эндоскопические подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на ключевые технические характеристики, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Тележку подбирают не отдельно, а под конкретный набор блоков: важно, чтобы процессор, источник света и монитор встали по весу и габаритам, а разъёмы и кабели не тянулись через всю стойку. Смотрю на устойчивость и колёсную базу — прибор часто катают, и тормоз на двух колёсах по диагонали здесь не мелочь. Гладкие поверхности и стойкость к дезинфектантам определяют, насколько удобно стойку обрабатывать.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3938,13 +4034,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое тележки эндоскопические</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Тележки эндоскопические — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>Эндоскопическая тележка — мобильная приборная стойка, на которой размещают и перевозят компоненты эндоскопической системы: видеопроцессор, источник света, монитор, аспиратор. Многоуровневая конструкция с поворотными колёсами (два с тормозом по диагонали) обеспечивает эргономичный доступ и безопасную транспортировку между кабинетами и зоной обработки. При выборе учитывают совместимость с приборами по габаритам и весу, число полок, нагрузку на ярус, наличие креплений под монитор и кабель-менеджмент. В каталоге — приборные стойки Medtrade СМПП-01 и СМПП-02.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3981,13 +4077,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Назначение эндоскопической тележки</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (технические параметры), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Эндоскопическая тележка служит для размещения, организации и безопасной транспортировки компонентов эндоскопической системы внутри медицинского учреждения. Она эргономично объединяет видеопроцессор, источник света, монитор, аспиратор и аксессуары, сокращает время подготовки к исследованию за счёт быстрого доступа ко всему набору и упрощает санитарную обработку благодаря гладким поверхностям и модульной конструкции.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4024,13 +4120,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Конструктивные особенности</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Тележки изготавливают из антикоррозионных материалов — стали с порошковым покрытием, алюминия или ударопрочного пластика. Многоуровневая структура с усиленными стойками несёт несколько полок, колёсная база оснащена поворотными колёсами с резиновым ободом, два из которых по диагонали снабжены тормозом. Встроенные держатели и направляющие организуют кабели; предусматривают крепления под монитор, ёмкости и инструменты.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4067,13 +4163,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Виды тележек</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Базовые модели — простые многоуровневые стойки для хранения оборудования. Функциональные модульные системы дополняются кронштейнами под мониторы, интеграцией видеокабелей и освещения. Узкоспециализированные тележки адаптированы под комплекты для конкретных областей (гастроэнтерология, урология, бронхоскопия). Контейнерные предназначены для транспортировки эндоскопов в лотках, снижая риск повреждения и перекрёстного загрязнения.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4090,6 +4186,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Критерии выбора</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>При подборе учитывают тип эндоскопической системы и совместимость по габаритам, весу и разъёмам; число полок и нагрузку на ярус; наличие креплений под монитор, ёмкости и инструменты; устойчивость и мобильность при работе в разных помещениях; легко очищаемые материалы, стойкие к дезинфектантам; возможность кастомизации под индивидуальную комплектацию. Эти параметры определяют, насколько удобно стойка встроится в рабочий процесс.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>telezhki_endoskopicheskie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
